--- a/others/LN-FN-MI.xlsx
+++ b/others/LN-FN-MI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\nibt\others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D746FDA-0176-4F7E-959B-3C96EBADA040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A790C7-9095-4AD0-8ADC-2460334F492F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1035" yWindow="1980" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>LASTNAME</t>
   </si>
@@ -31,191 +31,239 @@
     <t>MIDDLENAME</t>
   </si>
   <si>
-    <t>Leonardo</t>
-  </si>
-  <si>
-    <t>Rodriguez</t>
-  </si>
-  <si>
-    <t>Abunda</t>
-  </si>
-  <si>
-    <t>Jolly Roxane</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
-    <t>Jefferson</t>
-  </si>
-  <si>
-    <t>Ayhon</t>
-  </si>
-  <si>
-    <t>Adrianne</t>
-  </si>
-  <si>
-    <t>Ayuban</t>
-  </si>
-  <si>
-    <t>Barrozo</t>
-  </si>
-  <si>
-    <t>Eamaris</t>
-  </si>
-  <si>
-    <t>Montilla</t>
-  </si>
-  <si>
-    <t>Bate</t>
-  </si>
-  <si>
-    <t>Trisha</t>
-  </si>
-  <si>
-    <t>Giedjette</t>
-  </si>
-  <si>
-    <t>Bea</t>
-  </si>
-  <si>
-    <t>Maynard</t>
-  </si>
-  <si>
-    <t>Pica</t>
-  </si>
-  <si>
-    <t>Cabueñas</t>
-  </si>
-  <si>
-    <t>Mariss</t>
-  </si>
-  <si>
-    <t>Pasco</t>
-  </si>
-  <si>
-    <t>Erap</t>
-  </si>
-  <si>
-    <t>De Guzman</t>
-  </si>
-  <si>
-    <t>Nikko</t>
-  </si>
-  <si>
-    <t>Gabalfin</t>
-  </si>
-  <si>
-    <t>Coleene</t>
-  </si>
-  <si>
     <t>Alfonso</t>
   </si>
   <si>
-    <t>Hernandez</t>
-  </si>
-  <si>
-    <t>Crisette</t>
-  </si>
-  <si>
-    <t>Ibuyat</t>
-  </si>
-  <si>
-    <t>Christian</t>
-  </si>
-  <si>
-    <t>Cristina</t>
-  </si>
-  <si>
-    <t>Erika</t>
-  </si>
-  <si>
-    <t>Donalyn</t>
-  </si>
-  <si>
-    <t>Limson</t>
-  </si>
-  <si>
-    <t>Jay Charles</t>
-  </si>
-  <si>
-    <t>Padilla</t>
-  </si>
-  <si>
-    <t>Jasmine Marie</t>
-  </si>
-  <si>
-    <t>Mejico</t>
-  </si>
-  <si>
-    <t>Emerson</t>
-  </si>
-  <si>
-    <t>Mendoza</t>
-  </si>
-  <si>
-    <t>Mortel</t>
-  </si>
-  <si>
-    <t>Michelle</t>
-  </si>
-  <si>
-    <t>Paule</t>
-  </si>
-  <si>
-    <t>Narvaez</t>
-  </si>
-  <si>
-    <t>Ericjohn</t>
-  </si>
-  <si>
-    <t>Arguelles</t>
-  </si>
-  <si>
-    <t>Oronos</t>
-  </si>
-  <si>
-    <t>King John</t>
-  </si>
-  <si>
-    <t>Rosales</t>
-  </si>
-  <si>
-    <t>Ortega</t>
-  </si>
-  <si>
-    <t>Roselyn</t>
-  </si>
-  <si>
-    <t>Agustin</t>
-  </si>
-  <si>
-    <t>John Michael</t>
-  </si>
-  <si>
-    <t>Mijares</t>
-  </si>
-  <si>
-    <t>Saya</t>
-  </si>
-  <si>
-    <t>Michael</t>
-  </si>
-  <si>
-    <t>Olayao</t>
-  </si>
-  <si>
     <t>.</t>
   </si>
   <si>
     <t>MOBILE</t>
+  </si>
+  <si>
+    <t>Badiana</t>
+  </si>
+  <si>
+    <t>Kherby</t>
+  </si>
+  <si>
+    <t>Duran</t>
+  </si>
+  <si>
+    <t>Basañez Jr.</t>
+  </si>
+  <si>
+    <t>Epifanio</t>
+  </si>
+  <si>
+    <t>Alinsod</t>
+  </si>
+  <si>
+    <t>Basañez</t>
+  </si>
+  <si>
+    <t>Violeta</t>
+  </si>
+  <si>
+    <t>Castillo</t>
+  </si>
+  <si>
+    <t>Billones</t>
+  </si>
+  <si>
+    <t>Arlyne</t>
+  </si>
+  <si>
+    <t>De Luna</t>
+  </si>
+  <si>
+    <t>Bronzal</t>
+  </si>
+  <si>
+    <t>Hazel Joyce</t>
+  </si>
+  <si>
+    <t>Samson</t>
+  </si>
+  <si>
+    <t>Bulan</t>
+  </si>
+  <si>
+    <t>Rea</t>
+  </si>
+  <si>
+    <t>Gratol</t>
+  </si>
+  <si>
+    <t>Ching</t>
+  </si>
+  <si>
+    <t>John Vincent</t>
+  </si>
+  <si>
+    <t>Cuartocruz</t>
+  </si>
+  <si>
+    <t>Raffy</t>
+  </si>
+  <si>
+    <t>Dela Cruz</t>
+  </si>
+  <si>
+    <t>Dañas</t>
+  </si>
+  <si>
+    <t>Mikka</t>
+  </si>
+  <si>
+    <t>Bantog</t>
+  </si>
+  <si>
+    <t>Fortes</t>
+  </si>
+  <si>
+    <t>Cherry</t>
+  </si>
+  <si>
+    <t>Fungo</t>
+  </si>
+  <si>
+    <t>Guzman</t>
+  </si>
+  <si>
+    <t>Zabian Allen</t>
+  </si>
+  <si>
+    <t>Cacal</t>
+  </si>
+  <si>
+    <t>Limcolioc</t>
+  </si>
+  <si>
+    <t>Roiz Camille</t>
+  </si>
+  <si>
+    <t>Toribio</t>
+  </si>
+  <si>
+    <t>Lipata</t>
+  </si>
+  <si>
+    <t>Pamela Kaye</t>
+  </si>
+  <si>
+    <t>Adonis</t>
+  </si>
+  <si>
+    <t>Marañon</t>
+  </si>
+  <si>
+    <t>Bianchie Gwen</t>
+  </si>
+  <si>
+    <t>Calar</t>
+  </si>
+  <si>
+    <t>Martirez</t>
+  </si>
+  <si>
+    <t>Royce</t>
+  </si>
+  <si>
+    <t>Bermejo</t>
+  </si>
+  <si>
+    <t>Modrigo</t>
+  </si>
+  <si>
+    <t>Maureen Joy</t>
+  </si>
+  <si>
+    <t>Acedo</t>
+  </si>
+  <si>
+    <t>Nate</t>
+  </si>
+  <si>
+    <t>Jayson</t>
+  </si>
+  <si>
+    <t>Guiriba</t>
+  </si>
+  <si>
+    <t>Obsiman</t>
+  </si>
+  <si>
+    <t>Maxine</t>
+  </si>
+  <si>
+    <t>Suson</t>
+  </si>
+  <si>
+    <t>Quiapos</t>
+  </si>
+  <si>
+    <t>Maria Rosemarie</t>
+  </si>
+  <si>
+    <t>Maneja</t>
+  </si>
+  <si>
+    <t>Reyes</t>
+  </si>
+  <si>
+    <t>Mary Rose</t>
+  </si>
+  <si>
+    <t>Rosete</t>
+  </si>
+  <si>
+    <t>Jeannine Tricia</t>
+  </si>
+  <si>
+    <t>Gacutan</t>
+  </si>
+  <si>
+    <t>Sabuco</t>
+  </si>
+  <si>
+    <t>Helen Grace</t>
+  </si>
+  <si>
+    <t>Orogo</t>
+  </si>
+  <si>
+    <t>Sucgang</t>
+  </si>
+  <si>
+    <t>Anne Shaina Catrina</t>
+  </si>
+  <si>
+    <t>Paqueros</t>
+  </si>
+  <si>
+    <t>Ventura</t>
+  </si>
+  <si>
+    <t>Ma. Loraine</t>
+  </si>
+  <si>
+    <t>Patillas</t>
+  </si>
+  <si>
+    <t>Villareal</t>
+  </si>
+  <si>
+    <t>Zyril Jane Veronique</t>
+  </si>
+  <si>
+    <t>Flores</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -241,18 +289,25 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI Historic"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -302,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -314,72 +369,23 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -407,9 +413,9 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Sheet1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" dxfId="6"/>
-      <tableStyleElement type="secondRowStripe" dxfId="5"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -424,12 +430,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D26" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D26">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="LASTNAME" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="FIRSTNAME " dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="MIDDLENAME" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{2D1941A2-CF46-450C-80CD-F6DE170864A9}" name="MOBILE" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="LASTNAME"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="FIRSTNAME "/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="MIDDLENAME"/>
+    <tableColumn id="4" xr3:uid="{2D1941A2-CF46-450C-80CD-F6DE170864A9}" name="MOBILE"/>
   </tableColumns>
   <tableStyleInfo name="Sheet1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -654,358 +660,358 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>62</v>
+      <c r="D1" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4">
-        <v>9164443422</v>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5">
+        <v>9944702560</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="4">
-        <v>9293577569</v>
+        <v>11</v>
+      </c>
+      <c r="D3" s="6">
+        <v>9611896615</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="4">
-        <v>9156229308</v>
+        <v>14</v>
+      </c>
+      <c r="D4" s="6">
+        <v>9984585850</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="4">
-        <v>9956583198</v>
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="5">
+        <v>9754939101</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="4">
-        <v>9776473230</v>
+        <v>20</v>
+      </c>
+      <c r="D6" s="6">
+        <v>9273781582</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="4">
-        <v>9171154766</v>
+        <v>23</v>
+      </c>
+      <c r="D7" s="5">
+        <v>9984010088</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="4">
-        <v>9915462501</v>
+        <v>25</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="6">
+        <v>9944680405</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="4">
-        <v>9214977899</v>
+        <v>28</v>
+      </c>
+      <c r="D9" s="6">
+        <v>9543223148</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="4">
-        <v>9127133793</v>
+        <v>31</v>
+      </c>
+      <c r="D10" s="6">
+        <v>9914155264</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="4">
-        <v>9267428998</v>
+      <c r="A11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="5">
+        <v>9453213313</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="4">
-        <v>9566343454</v>
+        <v>37</v>
+      </c>
+      <c r="D12" s="6">
+        <v>9931992903</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="4">
-        <v>9568504933</v>
+        <v>40</v>
+      </c>
+      <c r="D13" s="6">
+        <v>9653009016</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="4">
-        <v>9157592715</v>
+        <v>43</v>
+      </c>
+      <c r="D14" s="5">
+        <v>9424965764</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="4">
-        <v>9563642459</v>
+        <v>44</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="6">
+        <v>9950117499</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="4">
-        <v>9910360679</v>
+      <c r="A16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="8">
+        <v>9368919175</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="4">
-        <v>9957145622</v>
+        <v>52</v>
+      </c>
+      <c r="D17" s="5">
+        <v>9654213378</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="4">
-        <v>9056117306</v>
+        <v>55</v>
+      </c>
+      <c r="D18" s="6">
+        <v>9318830436</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="4">
-        <v>9771959537</v>
+      <c r="A19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="6">
+        <v>9916697845</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="4">
-        <v>9129391047</v>
+        <v>61</v>
+      </c>
+      <c r="D20" s="6">
+        <v>9928746364</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="4">
-        <v>9494272505</v>
+        <v>3</v>
+      </c>
+      <c r="D21" s="6">
+        <v>9153634656</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22" s="4">
-        <v>9519143986</v>
+        <v>66</v>
+      </c>
+      <c r="D22" s="6">
+        <v>9674635510</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="4">
-        <v>9932021295</v>
+        <v>69</v>
+      </c>
+      <c r="D23" s="6">
+        <v>9469540914</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="4">
-        <v>9975793056</v>
+        <v>72</v>
+      </c>
+      <c r="D24" s="6">
+        <v>9639810093</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="4">
-        <v>9914253443</v>
+        <v>75</v>
+      </c>
+      <c r="D25" s="6">
+        <v>9297802605</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D26" s="4">
-        <v>9852674174</v>
+        <v>78</v>
+      </c>
+      <c r="D26" s="6">
+        <v>9099140650</v>
       </c>
     </row>
   </sheetData>
